--- a/data/la_penita.xlsx
+++ b/data/la_penita.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,30 +457,50 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>05dec2025</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>06dec2025</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>07dec2025</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>08dec2025</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>25nov2025</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -508,18 +528,30 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
         <v>1</v>
       </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -545,18 +577,30 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
+        <v>16</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>10</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="n">
         <v>9</v>
       </c>
-      <c r="H3" t="n">
+      <c r="L3" t="n">
         <v>9</v>
       </c>
-      <c r="I3" t="n">
+      <c r="M3" t="n">
         <v>19</v>
       </c>
-      <c r="J3" t="n">
+      <c r="N3" t="n">
         <v>11</v>
       </c>
-      <c r="K3" t="n">
+      <c r="O3" t="n">
         <v>18</v>
       </c>
     </row>
@@ -579,21 +623,33 @@
         <v>8</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G4" t="n">
+        <v>20</v>
+      </c>
+      <c r="H4" t="n">
+        <v>10</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
         <v>13</v>
       </c>
-      <c r="H4" t="n">
-        <v>10</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
+        <v>10</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
         <v>15</v>
       </c>
-      <c r="K4" t="n">
+      <c r="O4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -619,18 +675,30 @@
         <v>3</v>
       </c>
       <c r="G5" t="n">
+        <v>7</v>
+      </c>
+      <c r="H5" t="n">
+        <v>29</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K5" t="n">
         <v>1</v>
       </c>
-      <c r="H5" t="n">
+      <c r="L5" t="n">
         <v>19</v>
       </c>
-      <c r="I5" t="n">
+      <c r="M5" t="n">
         <v>11</v>
       </c>
-      <c r="J5" t="n">
+      <c r="N5" t="n">
         <v>19</v>
       </c>
-      <c r="K5" t="n">
+      <c r="O5" t="n">
         <v>26</v>
       </c>
     </row>
@@ -653,21 +721,33 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -707,6 +787,18 @@
       <c r="K7" t="n">
         <v>0</v>
       </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -727,21 +819,33 @@
         <v>10</v>
       </c>
       <c r="F8" t="n">
+        <v>15</v>
+      </c>
+      <c r="G8" t="n">
+        <v>11</v>
+      </c>
+      <c r="H8" t="n">
+        <v>19</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
         <v>3</v>
       </c>
-      <c r="G8" t="n">
-        <v>10</v>
-      </c>
-      <c r="H8" t="n">
+      <c r="K8" t="n">
+        <v>10</v>
+      </c>
+      <c r="L8" t="n">
         <v>11</v>
       </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
         <v>25</v>
       </c>
-      <c r="K8" t="n">
+      <c r="O8" t="n">
         <v>21</v>
       </c>
     </row>
@@ -764,21 +868,33 @@
         <v>15</v>
       </c>
       <c r="F9" t="n">
+        <v>10</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
         <v>5</v>
       </c>
-      <c r="G9" t="n">
-        <v>10</v>
-      </c>
-      <c r="H9" t="n">
+      <c r="K9" t="n">
+        <v>10</v>
+      </c>
+      <c r="L9" t="n">
         <v>15</v>
       </c>
-      <c r="I9" t="n">
+      <c r="M9" t="n">
         <v>17</v>
       </c>
-      <c r="J9" t="n">
-        <v>10</v>
-      </c>
-      <c r="K9" t="n">
+      <c r="N9" t="n">
+        <v>10</v>
+      </c>
+      <c r="O9" t="n">
         <v>18</v>
       </c>
     </row>
@@ -801,21 +917,33 @@
         <v>32</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G10" t="n">
+        <v>10</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>25</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
         <v>14</v>
       </c>
-      <c r="H10" t="n">
+      <c r="L10" t="n">
         <v>11</v>
       </c>
-      <c r="I10" t="n">
+      <c r="M10" t="n">
         <v>14</v>
       </c>
-      <c r="J10" t="n">
+      <c r="N10" t="n">
         <v>3</v>
       </c>
-      <c r="K10" t="n">
+      <c r="O10" t="n">
         <v>21</v>
       </c>
     </row>
@@ -838,21 +966,33 @@
         <v>8</v>
       </c>
       <c r="F11" t="n">
+        <v>3</v>
+      </c>
+      <c r="G11" t="n">
+        <v>20</v>
+      </c>
+      <c r="H11" t="n">
+        <v>17</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
         <v>2</v>
       </c>
-      <c r="G11" t="n">
+      <c r="K11" t="n">
         <v>11</v>
       </c>
-      <c r="H11" t="n">
-        <v>10</v>
-      </c>
-      <c r="I11" t="n">
+      <c r="L11" t="n">
+        <v>10</v>
+      </c>
+      <c r="M11" t="n">
         <v>11</v>
       </c>
-      <c r="J11" t="n">
+      <c r="N11" t="n">
         <v>18</v>
       </c>
-      <c r="K11" t="n">
+      <c r="O11" t="n">
         <v>26</v>
       </c>
     </row>
@@ -875,21 +1015,33 @@
         <v>10</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G12" t="n">
+        <v>10</v>
+      </c>
+      <c r="H12" t="n">
         <v>13</v>
       </c>
-      <c r="H12" t="n">
-        <v>10</v>
-      </c>
       <c r="I12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
+        <v>13</v>
+      </c>
+      <c r="L12" t="n">
+        <v>10</v>
+      </c>
+      <c r="M12" t="n">
+        <v>10</v>
+      </c>
+      <c r="N12" t="n">
+        <v>10</v>
+      </c>
+      <c r="O12" t="n">
         <v>14</v>
       </c>
     </row>
@@ -912,21 +1064,33 @@
         <v>14</v>
       </c>
       <c r="F13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="H13" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I13" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
         <v>2</v>
       </c>
       <c r="K13" t="n">
+        <v>10</v>
+      </c>
+      <c r="L13" t="n">
+        <v>10</v>
+      </c>
+      <c r="M13" t="n">
+        <v>10</v>
+      </c>
+      <c r="N13" t="n">
+        <v>2</v>
+      </c>
+      <c r="O13" t="n">
         <v>25</v>
       </c>
     </row>
@@ -949,21 +1113,33 @@
         <v>13</v>
       </c>
       <c r="F14" t="n">
+        <v>10</v>
+      </c>
+      <c r="G14" t="n">
+        <v>6</v>
+      </c>
+      <c r="H14" t="n">
+        <v>14</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
         <v>5</v>
       </c>
-      <c r="G14" t="n">
-        <v>10</v>
-      </c>
-      <c r="H14" t="n">
+      <c r="K14" t="n">
+        <v>10</v>
+      </c>
+      <c r="L14" t="n">
         <v>11</v>
       </c>
-      <c r="I14" t="n">
+      <c r="M14" t="n">
         <v>13</v>
       </c>
-      <c r="J14" t="n">
+      <c r="N14" t="n">
         <v>19</v>
       </c>
-      <c r="K14" t="n">
+      <c r="O14" t="n">
         <v>23</v>
       </c>
     </row>
@@ -978,7 +1154,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1009,30 +1185,50 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>05dec2025</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>06dec2025</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>07dec2025</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>08dec2025</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>25nov2025</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -1049,15 +1245,19 @@
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -1080,25 +1280,37 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>18</t>
         </is>
@@ -1126,24 +1338,40 @@
           <t>8</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -1174,25 +1402,41 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>26</t>
         </is>
@@ -1216,12 +1460,28 @@
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -1243,6 +1503,10 @@
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -1268,26 +1532,42 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>21</t>
         </is>
@@ -1317,30 +1597,38 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>18</t>
         </is>
@@ -1368,28 +1656,44 @@
           <t>32</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>21</t>
         </is>
@@ -1423,30 +1727,46 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>26</t>
         </is>
@@ -1478,28 +1798,44 @@
           <t>10</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="G12" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
         <is>
           <t>14</t>
         </is>
@@ -1531,32 +1867,44 @@
           <t>14</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>25</t>
         </is>
@@ -1590,30 +1938,46 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>23</t>
         </is>

--- a/data/la_penita.xlsx
+++ b/data/la_penita.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O14"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,30 +477,35 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>09dec2025</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>25nov2025</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -540,11 +545,11 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
         <v>1</v>
       </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
@@ -552,23 +557,26 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>CASTRO JUAREZ MARIA ISABEL</t>
+          <t>77911713</t>
         </is>
       </c>
       <c r="B3" t="n">
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -577,96 +585,102 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>18</v>
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>CHERO JUAREZ ANYELA TATIANA</t>
+          <t>CASTRO JUAREZ MARIA ISABEL</t>
         </is>
       </c>
       <c r="B4" t="n">
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="H4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N4" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>11</v>
+      </c>
+      <c r="P4" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>GARAVITO LEON IVONNE LISSETH</t>
+          <t>CHERO JUAREZ ANYELA TATIANA</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
         <v>8</v>
@@ -675,114 +689,120 @@
         <v>3</v>
       </c>
       <c r="G5" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="H5" t="n">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="M5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N5" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>26</v>
+        <v>15</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>MORENO PALACIOS DAMARIS VANESA</t>
+          <t>GARAVITO LEON IVONNE LISSETH</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>0</v>
       </c>
       <c r="C6" t="n">
-        <v>74</v>
+        <v>36</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F6" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>19</v>
+      </c>
+      <c r="P6" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>MORETO ESPINOZA JUAN ALBERTO</t>
+          <t>MORENO PALACIOS DAMARIS VANESA</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>74</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -797,311 +817,332 @@
         <v>0</v>
       </c>
       <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>NIÑO GUERRERO ANYELA MELINA</t>
+          <t>MORETO ESPINOZA JUAN ALBERTO</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>21</v>
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>PANTA MONZON SHIRLEY MARIBEL</t>
+          <t>NIÑO GUERRERO ANYELA MELINA</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="D9" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" t="n">
         <v>15</v>
       </c>
-      <c r="F9" t="n">
-        <v>10</v>
-      </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="J9" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="K9" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="L9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="M9" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="N9" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>18</v>
+        <v>25</v>
+      </c>
+      <c r="P9" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>PEREZ VEGA ANA YSABEL</t>
+          <t>PANTA MONZON SHIRLEY MARIBEL</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="E10" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F10" t="n">
+        <v>10</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>9</v>
+      </c>
+      <c r="K10" t="n">
+        <v>5</v>
+      </c>
+      <c r="L10" t="n">
+        <v>10</v>
+      </c>
+      <c r="M10" t="n">
         <v>15</v>
       </c>
-      <c r="G10" t="n">
-        <v>10</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="n">
-        <v>25</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>14</v>
-      </c>
-      <c r="L10" t="n">
-        <v>11</v>
-      </c>
-      <c r="M10" t="n">
-        <v>14</v>
-      </c>
       <c r="N10" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="O10" t="n">
-        <v>21</v>
+        <v>10</v>
+      </c>
+      <c r="P10" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>TIMOTEO BAYONA SHARYN LISSETH</t>
+          <t>PEREZ VEGA ANA YSABEL</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="C11" t="n">
+        <v>8</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>32</v>
+      </c>
+      <c r="F11" t="n">
         <v>15</v>
       </c>
-      <c r="D11" t="n">
-        <v>11</v>
-      </c>
-      <c r="E11" t="n">
-        <v>8</v>
-      </c>
-      <c r="F11" t="n">
-        <v>3</v>
-      </c>
       <c r="G11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J11" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="K11" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="M11" t="n">
         <v>11</v>
       </c>
       <c r="N11" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="O11" t="n">
-        <v>26</v>
+        <v>3</v>
+      </c>
+      <c r="P11" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>TIZON NUÑEZ FRESIA YAMILI</t>
+          <t>TIMOTEO BAYONA SHARYN LISSETH</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F12" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H12" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="K12" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="L12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M12" t="n">
         <v>10</v>
       </c>
       <c r="N12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O12" t="n">
-        <v>14</v>
+        <v>18</v>
+      </c>
+      <c r="P12" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>VALLE SILVA SUTMMER ORFELINDA</t>
+          <t>TIZON NUÑEZ FRESIA YAMILI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D13" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E13" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G13" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="H13" t="n">
         <v>13</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J13" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="K13" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="M13" t="n">
         <v>10</v>
       </c>
       <c r="N13" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="O13" t="n">
-        <v>25</v>
+        <v>10</v>
+      </c>
+      <c r="P13" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>ZAPATA ZETA ROSA ARACELI</t>
+          <t>VALLE SILVA SUTMMER ORFELINDA</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
         <v>11</v>
@@ -1110,36 +1151,91 @@
         <v>12</v>
       </c>
       <c r="E14" t="n">
+        <v>14</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>24</v>
+      </c>
+      <c r="H14" t="n">
         <v>13</v>
       </c>
-      <c r="F14" t="n">
-        <v>10</v>
-      </c>
-      <c r="G14" t="n">
+      <c r="I14" t="n">
+        <v>13</v>
+      </c>
+      <c r="J14" t="n">
+        <v>15</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2</v>
+      </c>
+      <c r="L14" t="n">
+        <v>10</v>
+      </c>
+      <c r="M14" t="n">
+        <v>10</v>
+      </c>
+      <c r="N14" t="n">
+        <v>10</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2</v>
+      </c>
+      <c r="P14" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>ZAPATA ZETA ROSA ARACELI</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>20</v>
+      </c>
+      <c r="C15" t="n">
+        <v>11</v>
+      </c>
+      <c r="D15" t="n">
+        <v>12</v>
+      </c>
+      <c r="E15" t="n">
+        <v>13</v>
+      </c>
+      <c r="F15" t="n">
+        <v>10</v>
+      </c>
+      <c r="G15" t="n">
         <v>6</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H15" t="n">
         <v>14</v>
       </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
+      <c r="I15" t="n">
+        <v>12</v>
+      </c>
+      <c r="J15" t="n">
+        <v>27</v>
+      </c>
+      <c r="K15" t="n">
         <v>5</v>
       </c>
-      <c r="K14" t="n">
-        <v>10</v>
-      </c>
-      <c r="L14" t="n">
+      <c r="L15" t="n">
+        <v>10</v>
+      </c>
+      <c r="M15" t="n">
         <v>11</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N15" t="n">
         <v>13</v>
       </c>
-      <c r="N14" t="n">
+      <c r="O15" t="n">
         <v>19</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P15" t="n">
         <v>23</v>
       </c>
     </row>
@@ -1154,7 +1250,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O14"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1205,30 +1301,35 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>09dec2025</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>25nov2025</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -1249,145 +1350,116 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>CASTRO JUAREZ MARIA ISABEL</t>
+          <t>77911713</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>CHERO JUAREZ ANYELA TATIANA</t>
+          <t>CASTRO JUAREZ MARIA ISABEL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>GARAVITO LEON IVONNE LISSETH</t>
+          <t>CHERO JUAREZ ANYELA TATIANA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>23</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1402,427 +1474,454 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>20</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>13</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
-          <t>26</t>
-        </is>
-      </c>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>MORENO PALACIOS DAMARIS VANESA</t>
+          <t>GARAVITO LEON IVONNE LISSETH</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>36</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>MORETO ESPINOZA JUAN ALBERTO</t>
+          <t>MORENO PALACIOS DAMARIS VANESA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>NIÑO GUERRERO ANYELA MELINA</t>
+          <t>MORETO ESPINOZA JUAN ALBERTO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>PANTA MONZON SHIRLEY MARIBEL</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>NIÑO GUERRERO ANYELA MELINA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>21</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>PEREZ VEGA ANA YSABEL</t>
+          <t>PANTA MONZON SHIRLEY MARIBEL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>17</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>18</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>TIMOTEO BAYONA SHARYN LISSETH</t>
+          <t>PEREZ VEGA ANA YSABEL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
           <t>21</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>26</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>TIZON NUÑEZ FRESIA YAMILI</t>
+          <t>TIMOTEO BAYONA SHARYN LISSETH</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1832,152 +1931,253 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>26</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>VALLE SILVA SUTMMER ORFELINDA</t>
+          <t>TIZON NUÑEZ FRESIA YAMILI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
           <t>14</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>25</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
+          <t>VALLE SILVA SUTMMER ORFELINDA</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
           <t>ZAPATA ZETA ROSA ARACELI</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>23</t>
         </is>

--- a/data/la_penita.xlsx
+++ b/data/la_penita.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P15"/>
+  <dimension ref="A1:R15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,30 +482,40 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>10dec2025</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>11dec2025</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>25nov2025</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -548,18 +558,24 @@
         <v>0</v>
       </c>
       <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
         <v>1</v>
       </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -614,6 +630,12 @@
       <c r="P3" t="n">
         <v>0</v>
       </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -649,21 +671,27 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
         <v>9</v>
       </c>
-      <c r="M4" t="n">
+      <c r="O4" t="n">
         <v>9</v>
       </c>
-      <c r="N4" t="n">
+      <c r="P4" t="n">
         <v>19</v>
       </c>
-      <c r="O4" t="n">
+      <c r="Q4" t="n">
         <v>11</v>
       </c>
-      <c r="P4" t="n">
+      <c r="R4" t="n">
         <v>18</v>
       </c>
     </row>
@@ -701,21 +729,27 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
         <v>13</v>
       </c>
-      <c r="M5" t="n">
-        <v>10</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
       <c r="O5" t="n">
+        <v>10</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
         <v>15</v>
       </c>
-      <c r="P5" t="n">
+      <c r="R5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -753,21 +787,27 @@
         <v>38</v>
       </c>
       <c r="K6" t="n">
+        <v>10</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
         <v>3</v>
       </c>
-      <c r="L6" t="n">
+      <c r="N6" t="n">
         <v>1</v>
-      </c>
-      <c r="M6" t="n">
-        <v>19</v>
-      </c>
-      <c r="N6" t="n">
-        <v>11</v>
       </c>
       <c r="O6" t="n">
         <v>19</v>
       </c>
       <c r="P6" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>19</v>
+      </c>
+      <c r="R6" t="n">
         <v>26</v>
       </c>
     </row>
@@ -805,7 +845,7 @@
         <v>15</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -820,6 +860,12 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -874,6 +920,12 @@
       <c r="P8" t="n">
         <v>0</v>
       </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -909,21 +961,27 @@
         <v>11</v>
       </c>
       <c r="K9" t="n">
+        <v>10</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
         <v>3</v>
       </c>
-      <c r="L9" t="n">
-        <v>10</v>
-      </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
+        <v>10</v>
+      </c>
+      <c r="O9" t="n">
         <v>11</v>
       </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
         <v>25</v>
       </c>
-      <c r="P9" t="n">
+      <c r="R9" t="n">
         <v>21</v>
       </c>
     </row>
@@ -961,21 +1019,27 @@
         <v>9</v>
       </c>
       <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>6</v>
+      </c>
+      <c r="M10" t="n">
         <v>5</v>
       </c>
-      <c r="L10" t="n">
-        <v>10</v>
-      </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
+        <v>10</v>
+      </c>
+      <c r="O10" t="n">
         <v>15</v>
       </c>
-      <c r="N10" t="n">
+      <c r="P10" t="n">
         <v>17</v>
       </c>
-      <c r="O10" t="n">
-        <v>10</v>
-      </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
+        <v>10</v>
+      </c>
+      <c r="R10" t="n">
         <v>18</v>
       </c>
     </row>
@@ -1013,21 +1077,27 @@
         <v>13</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="L11" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="M11" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
         <v>14</v>
       </c>
       <c r="O11" t="n">
+        <v>11</v>
+      </c>
+      <c r="P11" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q11" t="n">
         <v>3</v>
       </c>
-      <c r="P11" t="n">
+      <c r="R11" t="n">
         <v>21</v>
       </c>
     </row>
@@ -1065,21 +1135,27 @@
         <v>50</v>
       </c>
       <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>10</v>
+      </c>
+      <c r="M12" t="n">
         <v>2</v>
-      </c>
-      <c r="L12" t="n">
-        <v>11</v>
-      </c>
-      <c r="M12" t="n">
-        <v>10</v>
       </c>
       <c r="N12" t="n">
         <v>11</v>
       </c>
       <c r="O12" t="n">
+        <v>10</v>
+      </c>
+      <c r="P12" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q12" t="n">
         <v>18</v>
       </c>
-      <c r="P12" t="n">
+      <c r="R12" t="n">
         <v>26</v>
       </c>
     </row>
@@ -1120,18 +1196,24 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
+        <v>10</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
         <v>13</v>
       </c>
-      <c r="M13" t="n">
-        <v>10</v>
-      </c>
-      <c r="N13" t="n">
-        <v>10</v>
-      </c>
       <c r="O13" t="n">
         <v>10</v>
       </c>
       <c r="P13" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>10</v>
+      </c>
+      <c r="R13" t="n">
         <v>14</v>
       </c>
     </row>
@@ -1169,21 +1251,27 @@
         <v>15</v>
       </c>
       <c r="K14" t="n">
+        <v>15</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
         <v>2</v>
       </c>
-      <c r="L14" t="n">
-        <v>10</v>
-      </c>
-      <c r="M14" t="n">
-        <v>10</v>
-      </c>
       <c r="N14" t="n">
         <v>10</v>
       </c>
       <c r="O14" t="n">
+        <v>10</v>
+      </c>
+      <c r="P14" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q14" t="n">
         <v>2</v>
       </c>
-      <c r="P14" t="n">
+      <c r="R14" t="n">
         <v>25</v>
       </c>
     </row>
@@ -1221,21 +1309,27 @@
         <v>27</v>
       </c>
       <c r="K15" t="n">
+        <v>11</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
         <v>5</v>
       </c>
-      <c r="L15" t="n">
-        <v>10</v>
-      </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
+        <v>10</v>
+      </c>
+      <c r="O15" t="n">
         <v>11</v>
       </c>
-      <c r="N15" t="n">
+      <c r="P15" t="n">
         <v>13</v>
       </c>
-      <c r="O15" t="n">
+      <c r="Q15" t="n">
         <v>19</v>
       </c>
-      <c r="P15" t="n">
+      <c r="R15" t="n">
         <v>23</v>
       </c>
     </row>
@@ -1250,7 +1344,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P15"/>
+  <dimension ref="A1:R15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1306,30 +1400,40 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>10dec2025</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>11dec2025</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>25nov2025</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -1351,15 +1455,17 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -1386,6 +1492,8 @@
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -1418,28 +1526,34 @@
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>18</t>
         </is>
@@ -1488,24 +1602,30 @@
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -1556,30 +1676,36 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>26</t>
         </is>
@@ -1624,12 +1750,18 @@
           <t>15</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -1656,6 +1788,8 @@
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -1706,26 +1840,32 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>21</t>
         </is>
@@ -1766,32 +1906,38 @@
           <t>9</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
         <is>
           <t>18</t>
         </is>
@@ -1840,28 +1986,38 @@
           <t>13</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>21</t>
         </is>
@@ -1914,32 +2070,38 @@
           <t>50</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>26</t>
         </is>
@@ -1999,25 +2161,31 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="O13" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
         <is>
           <t>14</t>
         </is>
@@ -2072,19 +2240,15 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr">
         <is>
           <t>10</t>
@@ -2092,10 +2256,20 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>25</t>
         </is>
@@ -2154,30 +2328,36 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>23</t>
         </is>

--- a/data/la_penita.xlsx
+++ b/data/la_penita.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R15"/>
+  <dimension ref="A1:S15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -492,30 +492,35 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>12dec2025</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>25nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -564,11 +569,11 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
         <v>1</v>
       </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
@@ -576,6 +581,9 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -636,6 +644,9 @@
       <c r="R3" t="n">
         <v>0</v>
       </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -674,24 +685,27 @@
         <v>33</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>9</v>
       </c>
       <c r="P4" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q4" t="n">
         <v>19</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>11</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>18</v>
       </c>
     </row>
@@ -732,24 +746,27 @@
         <v>10</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
         <v>13</v>
       </c>
-      <c r="O5" t="n">
-        <v>10</v>
-      </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
         <v>15</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -790,24 +807,27 @@
         <v>10</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
         <v>3</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>1</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>19</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>11</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>19</v>
       </c>
-      <c r="R6" t="n">
+      <c r="S6" t="n">
         <v>26</v>
       </c>
     </row>
@@ -848,7 +868,7 @@
         <v>13</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -866,6 +886,9 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -926,6 +949,9 @@
       <c r="R8" t="n">
         <v>0</v>
       </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -964,24 +990,27 @@
         <v>10</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
         <v>3</v>
       </c>
-      <c r="N9" t="n">
-        <v>10</v>
-      </c>
       <c r="O9" t="n">
+        <v>10</v>
+      </c>
+      <c r="P9" t="n">
         <v>11</v>
       </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
       <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
         <v>25</v>
       </c>
-      <c r="R9" t="n">
+      <c r="S9" t="n">
         <v>21</v>
       </c>
     </row>
@@ -1022,24 +1051,27 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
         <v>5</v>
       </c>
-      <c r="N10" t="n">
-        <v>10</v>
-      </c>
       <c r="O10" t="n">
+        <v>10</v>
+      </c>
+      <c r="P10" t="n">
         <v>15</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>17</v>
       </c>
-      <c r="Q10" t="n">
-        <v>10</v>
-      </c>
       <c r="R10" t="n">
+        <v>10</v>
+      </c>
+      <c r="S10" t="n">
         <v>18</v>
       </c>
     </row>
@@ -1080,24 +1112,27 @@
         <v>17</v>
       </c>
       <c r="L11" t="n">
+        <v>7</v>
+      </c>
+      <c r="M11" t="n">
+        <v>9</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>14</v>
+      </c>
+      <c r="P11" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>14</v>
+      </c>
+      <c r="R11" t="n">
         <v>3</v>
       </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="n">
-        <v>14</v>
-      </c>
-      <c r="O11" t="n">
-        <v>11</v>
-      </c>
-      <c r="P11" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3</v>
-      </c>
-      <c r="R11" t="n">
+      <c r="S11" t="n">
         <v>21</v>
       </c>
     </row>
@@ -1138,24 +1173,27 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
         <v>2</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>11</v>
       </c>
-      <c r="O12" t="n">
-        <v>10</v>
-      </c>
       <c r="P12" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q12" t="n">
         <v>11</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>18</v>
       </c>
-      <c r="R12" t="n">
+      <c r="S12" t="n">
         <v>26</v>
       </c>
     </row>
@@ -1196,17 +1234,17 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
         <v>13</v>
       </c>
-      <c r="O13" t="n">
-        <v>10</v>
-      </c>
       <c r="P13" t="n">
         <v>10</v>
       </c>
@@ -1214,6 +1252,9 @@
         <v>10</v>
       </c>
       <c r="R13" t="n">
+        <v>10</v>
+      </c>
+      <c r="S13" t="n">
         <v>14</v>
       </c>
     </row>
@@ -1254,14 +1295,14 @@
         <v>15</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
         <v>2</v>
       </c>
-      <c r="N14" t="n">
-        <v>10</v>
-      </c>
       <c r="O14" t="n">
         <v>10</v>
       </c>
@@ -1269,9 +1310,12 @@
         <v>10</v>
       </c>
       <c r="Q14" t="n">
+        <v>10</v>
+      </c>
+      <c r="R14" t="n">
         <v>2</v>
       </c>
-      <c r="R14" t="n">
+      <c r="S14" t="n">
         <v>25</v>
       </c>
     </row>
@@ -1312,24 +1356,27 @@
         <v>11</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
         <v>5</v>
       </c>
-      <c r="N15" t="n">
-        <v>10</v>
-      </c>
       <c r="O15" t="n">
+        <v>10</v>
+      </c>
+      <c r="P15" t="n">
         <v>11</v>
       </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
         <v>13</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>19</v>
       </c>
-      <c r="R15" t="n">
+      <c r="S15" t="n">
         <v>23</v>
       </c>
     </row>
@@ -1344,7 +1391,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R15"/>
+  <dimension ref="A1:S15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1410,30 +1457,35 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>12dec2025</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>25nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -1457,15 +1509,16 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -1494,6 +1547,7 @@
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -1531,29 +1585,34 @@
           <t>33</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr">
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>18</t>
         </is>
@@ -1607,25 +1666,34 @@
           <t>10</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr">
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -1679,33 +1747,38 @@
           <t>10</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>26</t>
         </is>
@@ -1755,13 +1828,18 @@
           <t>13</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -1790,6 +1868,7 @@
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -1843,29 +1922,34 @@
           <t>10</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="O9" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr">
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>21</t>
         </is>
@@ -1909,35 +1993,36 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
+          <t>24</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="O10" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="R10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>18</t>
         </is>
@@ -1993,31 +2078,36 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>21</t>
         </is>
@@ -2073,35 +2163,36 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>26</t>
         </is>
@@ -2161,20 +2252,16 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>23</t>
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>10</t>
@@ -2186,6 +2273,11 @@
         </is>
       </c>
       <c r="R13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
         <is>
           <t>14</t>
         </is>
@@ -2243,17 +2335,17 @@
           <t>15</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="O14" t="inlineStr">
         <is>
           <t>10</t>
@@ -2266,10 +2358,15 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>25</t>
         </is>
@@ -2331,33 +2428,38 @@
           <t>11</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="O15" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>23</t>
         </is>

--- a/data/la_penita.xlsx
+++ b/data/la_penita.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S15"/>
+  <dimension ref="A1:U15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -497,30 +497,40 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>13dec2025</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>14dec2025</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
           <t>25nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -572,18 +582,24 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
         <v>1</v>
       </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
       <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -647,6 +663,12 @@
       <c r="S3" t="n">
         <v>0</v>
       </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -688,24 +710,30 @@
         <v>7</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
+        <v>14</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
         <v>9</v>
       </c>
-      <c r="P4" t="n">
+      <c r="R4" t="n">
         <v>9</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="S4" t="n">
         <v>19</v>
       </c>
-      <c r="R4" t="n">
+      <c r="T4" t="n">
         <v>11</v>
       </c>
-      <c r="S4" t="n">
+      <c r="U4" t="n">
         <v>18</v>
       </c>
     </row>
@@ -752,21 +780,27 @@
         <v>5</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O5" t="n">
+        <v>12</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
         <v>13</v>
       </c>
-      <c r="P5" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
+        <v>10</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
         <v>15</v>
       </c>
-      <c r="S5" t="n">
+      <c r="U5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -810,24 +844,30 @@
         <v>6</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="N6" t="n">
+        <v>8</v>
+      </c>
+      <c r="O6" t="n">
+        <v>17</v>
+      </c>
+      <c r="P6" t="n">
         <v>3</v>
       </c>
-      <c r="O6" t="n">
+      <c r="Q6" t="n">
         <v>1</v>
-      </c>
-      <c r="P6" t="n">
-        <v>19</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>11</v>
       </c>
       <c r="R6" t="n">
         <v>19</v>
       </c>
       <c r="S6" t="n">
+        <v>11</v>
+      </c>
+      <c r="T6" t="n">
+        <v>19</v>
+      </c>
+      <c r="U6" t="n">
         <v>26</v>
       </c>
     </row>
@@ -871,13 +911,13 @@
         <v>13</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -889,6 +929,12 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -952,6 +998,12 @@
       <c r="S8" t="n">
         <v>0</v>
       </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -996,21 +1048,27 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
+        <v>20</v>
+      </c>
+      <c r="O9" t="n">
+        <v>36</v>
+      </c>
+      <c r="P9" t="n">
         <v>3</v>
       </c>
-      <c r="O9" t="n">
-        <v>10</v>
-      </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
+        <v>10</v>
+      </c>
+      <c r="R9" t="n">
         <v>11</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
         <v>25</v>
       </c>
-      <c r="S9" t="n">
+      <c r="U9" t="n">
         <v>21</v>
       </c>
     </row>
@@ -1051,27 +1109,33 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="N10" t="n">
+        <v>17</v>
+      </c>
+      <c r="O10" t="n">
+        <v>10</v>
+      </c>
+      <c r="P10" t="n">
         <v>5</v>
       </c>
-      <c r="O10" t="n">
-        <v>10</v>
-      </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
+        <v>10</v>
+      </c>
+      <c r="R10" t="n">
         <v>15</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="S10" t="n">
         <v>17</v>
       </c>
-      <c r="R10" t="n">
-        <v>10</v>
-      </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
+        <v>10</v>
+      </c>
+      <c r="U10" t="n">
         <v>18</v>
       </c>
     </row>
@@ -1118,21 +1182,27 @@
         <v>9</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O11" t="n">
         <v>14</v>
       </c>
       <c r="P11" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>14</v>
       </c>
       <c r="R11" t="n">
+        <v>11</v>
+      </c>
+      <c r="S11" t="n">
+        <v>14</v>
+      </c>
+      <c r="T11" t="n">
         <v>3</v>
       </c>
-      <c r="S11" t="n">
+      <c r="U11" t="n">
         <v>21</v>
       </c>
     </row>
@@ -1176,24 +1246,30 @@
         <v>16</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N12" t="n">
+        <v>7</v>
+      </c>
+      <c r="O12" t="n">
+        <v>17</v>
+      </c>
+      <c r="P12" t="n">
         <v>2</v>
-      </c>
-      <c r="O12" t="n">
-        <v>11</v>
-      </c>
-      <c r="P12" t="n">
-        <v>10</v>
       </c>
       <c r="Q12" t="n">
         <v>11</v>
       </c>
       <c r="R12" t="n">
+        <v>10</v>
+      </c>
+      <c r="S12" t="n">
+        <v>11</v>
+      </c>
+      <c r="T12" t="n">
         <v>18</v>
       </c>
-      <c r="S12" t="n">
+      <c r="U12" t="n">
         <v>26</v>
       </c>
     </row>
@@ -1237,24 +1313,30 @@
         <v>23</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O13" t="n">
+        <v>12</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
         <v>13</v>
       </c>
-      <c r="P13" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>10</v>
-      </c>
       <c r="R13" t="n">
         <v>10</v>
       </c>
       <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="n">
+        <v>10</v>
+      </c>
+      <c r="U13" t="n">
         <v>14</v>
       </c>
     </row>
@@ -1298,24 +1380,30 @@
         <v>14</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="N14" t="n">
+        <v>18</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
         <v>2</v>
       </c>
-      <c r="O14" t="n">
-        <v>10</v>
-      </c>
-      <c r="P14" t="n">
-        <v>10</v>
-      </c>
       <c r="Q14" t="n">
         <v>10</v>
       </c>
       <c r="R14" t="n">
+        <v>10</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="n">
         <v>2</v>
       </c>
-      <c r="S14" t="n">
+      <c r="U14" t="n">
         <v>25</v>
       </c>
     </row>
@@ -1359,24 +1447,30 @@
         <v>14</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N15" t="n">
+        <v>18</v>
+      </c>
+      <c r="O15" t="n">
+        <v>22</v>
+      </c>
+      <c r="P15" t="n">
         <v>5</v>
       </c>
-      <c r="O15" t="n">
-        <v>10</v>
-      </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
+        <v>10</v>
+      </c>
+      <c r="R15" t="n">
         <v>11</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="S15" t="n">
         <v>13</v>
       </c>
-      <c r="R15" t="n">
+      <c r="T15" t="n">
         <v>19</v>
       </c>
-      <c r="S15" t="n">
+      <c r="U15" t="n">
         <v>23</v>
       </c>
     </row>
@@ -1391,7 +1485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S15"/>
+  <dimension ref="A1:U15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1462,30 +1556,40 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>13dec2025</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>14dec2025</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
           <t>25nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -1510,15 +1614,17 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr">
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -1548,6 +1654,8 @@
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -1590,29 +1698,39 @@
           <t>7</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>18</t>
         </is>
@@ -1676,24 +1794,34 @@
           <t>5</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="O5" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -1752,33 +1880,47 @@
           <t>6</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>26</t>
         </is>
@@ -1833,13 +1975,27 @@
           <t>13</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -1869,6 +2025,8 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -1930,26 +2088,36 @@
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>21</t>
         </is>
@@ -1993,36 +2161,50 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
         <is>
           <t>18</t>
         </is>
@@ -2086,28 +2268,38 @@
           <t>9</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="O11" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>21</t>
         </is>
@@ -2166,33 +2358,47 @@
           <t>16</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>26</t>
         </is>
@@ -2255,29 +2461,43 @@
           <t>23</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="O13" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="R13" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
         <is>
           <t>14</t>
         </is>
@@ -2340,22 +2560,22 @@
           <t>14</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="N14" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="Q14" t="inlineStr">
         <is>
           <t>10</t>
@@ -2363,10 +2583,20 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>25</t>
         </is>
@@ -2433,33 +2663,47 @@
           <t>14</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>23</t>
         </is>

--- a/data/la_penita.xlsx
+++ b/data/la_penita.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U15"/>
+  <dimension ref="A1:V15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,30 +507,35 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>15dec2025</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>25nov2025</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -588,11 +593,11 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
         <v>1</v>
       </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
@@ -600,6 +605,9 @@
         <v>0</v>
       </c>
       <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -669,6 +677,9 @@
       <c r="U3" t="n">
         <v>0</v>
       </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -722,18 +733,21 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>9</v>
       </c>
       <c r="S4" t="n">
+        <v>9</v>
+      </c>
+      <c r="T4" t="n">
         <v>19</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>11</v>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>18</v>
       </c>
     </row>
@@ -786,21 +800,24 @@
         <v>12</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
         <v>13</v>
       </c>
-      <c r="R5" t="n">
-        <v>10</v>
-      </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
         <v>15</v>
       </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -853,21 +870,24 @@
         <v>17</v>
       </c>
       <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
         <v>3</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>1</v>
       </c>
-      <c r="R6" t="n">
+      <c r="S6" t="n">
         <v>19</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>11</v>
       </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
         <v>19</v>
       </c>
-      <c r="U6" t="n">
+      <c r="V6" t="n">
         <v>26</v>
       </c>
     </row>
@@ -937,6 +957,9 @@
       <c r="U7" t="n">
         <v>0</v>
       </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -1004,6 +1027,9 @@
       <c r="U8" t="n">
         <v>0</v>
       </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -1054,21 +1080,24 @@
         <v>36</v>
       </c>
       <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
         <v>3</v>
       </c>
-      <c r="Q9" t="n">
-        <v>10</v>
-      </c>
       <c r="R9" t="n">
+        <v>10</v>
+      </c>
+      <c r="S9" t="n">
         <v>11</v>
       </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
       <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
         <v>25</v>
       </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
         <v>21</v>
       </c>
     </row>
@@ -1121,21 +1150,24 @@
         <v>10</v>
       </c>
       <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
         <v>5</v>
       </c>
-      <c r="Q10" t="n">
-        <v>10</v>
-      </c>
       <c r="R10" t="n">
+        <v>10</v>
+      </c>
+      <c r="S10" t="n">
         <v>15</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>17</v>
       </c>
-      <c r="T10" t="n">
-        <v>10</v>
-      </c>
       <c r="U10" t="n">
+        <v>10</v>
+      </c>
+      <c r="V10" t="n">
         <v>18</v>
       </c>
     </row>
@@ -1188,21 +1220,24 @@
         <v>14</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
         <v>14</v>
       </c>
-      <c r="R11" t="n">
+      <c r="S11" t="n">
         <v>11</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>14</v>
       </c>
-      <c r="T11" t="n">
+      <c r="U11" t="n">
         <v>3</v>
       </c>
-      <c r="U11" t="n">
+      <c r="V11" t="n">
         <v>21</v>
       </c>
     </row>
@@ -1255,21 +1290,24 @@
         <v>17</v>
       </c>
       <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
         <v>2</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>11</v>
       </c>
-      <c r="R12" t="n">
-        <v>10</v>
-      </c>
       <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="n">
         <v>11</v>
       </c>
-      <c r="T12" t="n">
+      <c r="U12" t="n">
         <v>18</v>
       </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
         <v>26</v>
       </c>
     </row>
@@ -1325,11 +1363,11 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
         <v>13</v>
       </c>
-      <c r="R13" t="n">
-        <v>10</v>
-      </c>
       <c r="S13" t="n">
         <v>10</v>
       </c>
@@ -1337,6 +1375,9 @@
         <v>10</v>
       </c>
       <c r="U13" t="n">
+        <v>10</v>
+      </c>
+      <c r="V13" t="n">
         <v>14</v>
       </c>
     </row>
@@ -1389,11 +1430,11 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q14" t="n">
         <v>2</v>
       </c>
-      <c r="Q14" t="n">
-        <v>10</v>
-      </c>
       <c r="R14" t="n">
         <v>10</v>
       </c>
@@ -1401,9 +1442,12 @@
         <v>10</v>
       </c>
       <c r="T14" t="n">
+        <v>10</v>
+      </c>
+      <c r="U14" t="n">
         <v>2</v>
       </c>
-      <c r="U14" t="n">
+      <c r="V14" t="n">
         <v>25</v>
       </c>
     </row>
@@ -1456,21 +1500,24 @@
         <v>22</v>
       </c>
       <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
         <v>5</v>
       </c>
-      <c r="Q15" t="n">
-        <v>10</v>
-      </c>
       <c r="R15" t="n">
+        <v>10</v>
+      </c>
+      <c r="S15" t="n">
         <v>11</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>13</v>
       </c>
-      <c r="T15" t="n">
+      <c r="U15" t="n">
         <v>19</v>
       </c>
-      <c r="U15" t="n">
+      <c r="V15" t="n">
         <v>23</v>
       </c>
     </row>
@@ -1485,7 +1532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U15"/>
+  <dimension ref="A1:V15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1566,30 +1613,35 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>15dec2025</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>25nov2025</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -1616,15 +1668,16 @@
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr">
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -1656,6 +1709,7 @@
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -1710,27 +1764,28 @@
         </is>
       </c>
       <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr">
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>18</t>
         </is>
@@ -1804,24 +1859,29 @@
           <t>12</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr">
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -1895,32 +1955,33 @@
           <t>17</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>26</t>
         </is>
@@ -1996,6 +2057,7 @@
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -2027,6 +2089,7 @@
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -2096,28 +2159,29 @@
           <t>36</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="R9" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr">
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>21</t>
         </is>
@@ -2179,32 +2243,33 @@
           <t>10</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="R10" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="U10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>18</t>
         </is>
@@ -2278,28 +2343,33 @@
           <t>14</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr">
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>21</t>
         </is>
@@ -2373,32 +2443,33 @@
           <t>17</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="S12" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>26</t>
         </is>
@@ -2477,16 +2548,12 @@
         </is>
       </c>
       <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr">
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="S13" t="inlineStr">
         <is>
           <t>10</t>
@@ -2498,6 +2565,11 @@
         </is>
       </c>
       <c r="U13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
         <is>
           <t>14</t>
         </is>
@@ -2573,14 +2645,14 @@
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="R14" t="inlineStr">
         <is>
           <t>10</t>
@@ -2593,10 +2665,15 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>25</t>
         </is>
@@ -2678,32 +2755,33 @@
           <t>22</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="R15" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>23</t>
         </is>

--- a/data/la_penita.xlsx
+++ b/data/la_penita.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V15"/>
+  <dimension ref="A1:W15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -512,30 +512,35 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
+          <t>16dec2025</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>25nov2025</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -596,11 +601,11 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
         <v>1</v>
       </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
       <c r="T2" t="n">
         <v>0</v>
       </c>
@@ -608,6 +613,9 @@
         <v>0</v>
       </c>
       <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -680,6 +688,9 @@
       <c r="V3" t="n">
         <v>0</v>
       </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -733,21 +744,24 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="R4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>9</v>
       </c>
       <c r="T4" t="n">
+        <v>9</v>
+      </c>
+      <c r="U4" t="n">
         <v>19</v>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>11</v>
       </c>
-      <c r="V4" t="n">
+      <c r="W4" t="n">
         <v>18</v>
       </c>
     </row>
@@ -806,18 +820,21 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
         <v>13</v>
       </c>
-      <c r="S5" t="n">
-        <v>10</v>
-      </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
         <v>15</v>
       </c>
-      <c r="V5" t="n">
+      <c r="W5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -873,21 +890,24 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
         <v>3</v>
       </c>
-      <c r="R6" t="n">
+      <c r="S6" t="n">
         <v>1</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>19</v>
       </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
         <v>11</v>
       </c>
-      <c r="U6" t="n">
+      <c r="V6" t="n">
         <v>19</v>
       </c>
-      <c r="V6" t="n">
+      <c r="W6" t="n">
         <v>26</v>
       </c>
     </row>
@@ -960,6 +980,9 @@
       <c r="V7" t="n">
         <v>0</v>
       </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -1030,6 +1053,9 @@
       <c r="V8" t="n">
         <v>0</v>
       </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -1083,21 +1109,24 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
         <v>3</v>
       </c>
-      <c r="R9" t="n">
-        <v>10</v>
-      </c>
       <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="n">
         <v>11</v>
       </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
       <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
         <v>25</v>
       </c>
-      <c r="V9" t="n">
+      <c r="W9" t="n">
         <v>21</v>
       </c>
     </row>
@@ -1153,21 +1182,24 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
         <v>5</v>
       </c>
-      <c r="R10" t="n">
-        <v>10</v>
-      </c>
       <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="n">
         <v>15</v>
       </c>
-      <c r="T10" t="n">
+      <c r="U10" t="n">
         <v>17</v>
       </c>
-      <c r="U10" t="n">
-        <v>10</v>
-      </c>
       <c r="V10" t="n">
+        <v>10</v>
+      </c>
+      <c r="W10" t="n">
         <v>18</v>
       </c>
     </row>
@@ -1226,18 +1258,21 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
         <v>14</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>11</v>
       </c>
-      <c r="T11" t="n">
+      <c r="U11" t="n">
         <v>14</v>
       </c>
-      <c r="U11" t="n">
+      <c r="V11" t="n">
         <v>3</v>
       </c>
-      <c r="V11" t="n">
+      <c r="W11" t="n">
         <v>21</v>
       </c>
     </row>
@@ -1293,21 +1328,24 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
         <v>2</v>
       </c>
-      <c r="R12" t="n">
+      <c r="S12" t="n">
         <v>11</v>
       </c>
-      <c r="S12" t="n">
-        <v>10</v>
-      </c>
       <c r="T12" t="n">
+        <v>10</v>
+      </c>
+      <c r="U12" t="n">
         <v>11</v>
       </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
         <v>18</v>
       </c>
-      <c r="V12" t="n">
+      <c r="W12" t="n">
         <v>26</v>
       </c>
     </row>
@@ -1366,11 +1404,11 @@
         <v>0</v>
       </c>
       <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
         <v>13</v>
       </c>
-      <c r="S13" t="n">
-        <v>10</v>
-      </c>
       <c r="T13" t="n">
         <v>10</v>
       </c>
@@ -1378,6 +1416,9 @@
         <v>10</v>
       </c>
       <c r="V13" t="n">
+        <v>10</v>
+      </c>
+      <c r="W13" t="n">
         <v>14</v>
       </c>
     </row>
@@ -1433,11 +1474,11 @@
         <v>14</v>
       </c>
       <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
         <v>2</v>
       </c>
-      <c r="R14" t="n">
-        <v>10</v>
-      </c>
       <c r="S14" t="n">
         <v>10</v>
       </c>
@@ -1445,9 +1486,12 @@
         <v>10</v>
       </c>
       <c r="U14" t="n">
+        <v>10</v>
+      </c>
+      <c r="V14" t="n">
         <v>2</v>
       </c>
-      <c r="V14" t="n">
+      <c r="W14" t="n">
         <v>25</v>
       </c>
     </row>
@@ -1503,21 +1547,24 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
         <v>5</v>
       </c>
-      <c r="R15" t="n">
-        <v>10</v>
-      </c>
       <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="n">
         <v>11</v>
       </c>
-      <c r="T15" t="n">
+      <c r="U15" t="n">
         <v>13</v>
       </c>
-      <c r="U15" t="n">
+      <c r="V15" t="n">
         <v>19</v>
       </c>
-      <c r="V15" t="n">
+      <c r="W15" t="n">
         <v>23</v>
       </c>
     </row>
@@ -1532,7 +1579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V15"/>
+  <dimension ref="A1:W15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1618,30 +1665,35 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
+          <t>16dec2025</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>25nov2025</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>26nov2025</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -1669,15 +1721,16 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr">
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -1710,6 +1763,7 @@
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -1764,28 +1818,33 @@
         </is>
       </c>
       <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>18</t>
         </is>
@@ -1865,23 +1924,24 @@
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr">
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr">
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -1956,32 +2016,33 @@
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr">
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>26</t>
         </is>
@@ -2058,6 +2119,7 @@
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -2090,6 +2152,7 @@
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -2160,28 +2223,29 @@
         </is>
       </c>
       <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr">
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="S9" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr">
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>21</t>
         </is>
@@ -2244,32 +2308,33 @@
         </is>
       </c>
       <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr">
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="S10" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="V10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
         <is>
           <t>18</t>
         </is>
@@ -2349,27 +2414,28 @@
         </is>
       </c>
       <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr">
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>21</t>
         </is>
@@ -2444,32 +2510,33 @@
         </is>
       </c>
       <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr">
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="T12" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>26</t>
         </is>
@@ -2549,16 +2616,12 @@
       </c>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr">
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="T13" t="inlineStr">
         <is>
           <t>10</t>
@@ -2570,6 +2633,11 @@
         </is>
       </c>
       <c r="V13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
         <is>
           <t>14</t>
         </is>
@@ -2648,16 +2716,12 @@
           <t>14</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="S14" t="inlineStr">
         <is>
           <t>10</t>
@@ -2670,10 +2734,15 @@
       </c>
       <c r="U14" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>25</t>
         </is>
@@ -2756,32 +2825,33 @@
         </is>
       </c>
       <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr">
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="S15" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>23</t>
         </is>
